--- a/docs/ai/test-cases/output/landing-scenarios-export.xlsx
+++ b/docs/ai/test-cases/output/landing-scenarios-export.xlsx
@@ -5385,7 +5385,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Generated: 2026-04-18T20:33:08.066Z</v>
+        <v>Generated: 2026-04-22T09:20:02.074Z</v>
       </c>
     </row>
     <row r="4">
